--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/Zwischenstände/YUKON_Datenbank/after_first_transformation_yukon.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/Zwischenstände/YUKON_Datenbank/after_first_transformation_yukon.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucca\OneDrive\SPEICHER\Hochschule\7. Semester\Abschlussarbeit Bearbeitung\Jupyter Notebooks\1_Data-Acquisition-Wrapper\Zwischenstände\YUKON_Datenbank\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D56997-A7BB-4552-A269-4A38A4B56460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="SHEET1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="203">
   <si>
     <t>X</t>
   </si>
@@ -634,8 +628,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -712,26 +706,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -769,7 +755,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -803,7 +789,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -838,10 +823,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1014,9 +998,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AH89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
@@ -1046,7 +1030,7 @@
     <col min="34" max="34" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1150,9 +1134,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34">
       <c r="A2">
-        <v>826060.71089999902</v>
+        <v>826060.710899999</v>
       </c>
       <c r="B2">
         <v>1007410.9552</v>
@@ -1197,18 +1181,18 @@
         <v>192</v>
       </c>
       <c r="AG2">
-        <v>63.405009999999997</v>
+        <v>63.40501</v>
       </c>
       <c r="AH2">
-        <v>-125.95569999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-125.9557</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34">
       <c r="A3">
-        <v>863603.56750000105</v>
+        <v>863603.5675000011</v>
       </c>
       <c r="B3">
-        <v>565896.20970000001</v>
+        <v>565896.2097</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1235,7 +1219,7 @@
         <v>34.4</v>
       </c>
       <c r="N3">
-        <v>16.399999999999999</v>
+        <v>16.4</v>
       </c>
       <c r="O3">
         <v>10.1</v>
@@ -1247,7 +1231,7 @@
         <v>592</v>
       </c>
       <c r="S3">
-        <v>94.1</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="T3">
         <v>16.7</v>
@@ -1262,18 +1246,18 @@
         <v>193</v>
       </c>
       <c r="AG3">
-        <v>59.427799999999998</v>
+        <v>59.4278</v>
       </c>
       <c r="AH3">
-        <v>-126.09892000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-126.09892</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34">
       <c r="A4">
-        <v>815862.70319999906</v>
+        <v>815862.7031999991</v>
       </c>
       <c r="B4">
-        <v>583973.50249999901</v>
+        <v>583973.502499999</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1321,18 +1305,18 @@
         <v>193</v>
       </c>
       <c r="AG4">
-        <v>59.630290000000002</v>
+        <v>59.63029</v>
       </c>
       <c r="AH4">
-        <v>-126.90672000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-126.90672</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34">
       <c r="A5">
-        <v>882034.31270000001</v>
+        <v>882034.3127</v>
       </c>
       <c r="B5">
-        <v>674476.08080000104</v>
+        <v>674476.080800001</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1377,7 +1361,7 @@
         <v>320</v>
       </c>
       <c r="Q5">
-        <v>94.1</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="R5">
         <v>3</v>
@@ -1410,18 +1394,18 @@
         <v>194</v>
       </c>
       <c r="AG5">
-        <v>60.381419999999999</v>
+        <v>60.38142</v>
       </c>
       <c r="AH5">
         <v>-125.56873</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34">
       <c r="A6">
-        <v>878957.37769999902</v>
+        <v>878957.377699999</v>
       </c>
       <c r="B6">
-        <v>662320.60990000004</v>
+        <v>662320.6099</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1493,18 +1477,18 @@
         <v>194</v>
       </c>
       <c r="AG6">
-        <v>60.275820000000003</v>
+        <v>60.27582</v>
       </c>
       <c r="AH6">
-        <v>-125.64785999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-125.64786</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34">
       <c r="A7">
-        <v>876614.64469999995</v>
+        <v>876614.6446999999</v>
       </c>
       <c r="B7">
-        <v>632326.04480000003</v>
+        <v>632326.0448</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1534,13 +1518,13 @@
         <v>256</v>
       </c>
       <c r="L7">
-        <v>67.900000000000006</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="M7">
         <v>21</v>
       </c>
       <c r="N7">
-        <v>4.0999999999999996</v>
+        <v>4.1</v>
       </c>
       <c r="O7">
         <v>1.7</v>
@@ -1555,7 +1539,7 @@
         <v>3</v>
       </c>
       <c r="T7">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="U7">
         <v>1.3</v>
@@ -1582,13 +1566,13 @@
         <v>194</v>
       </c>
       <c r="AG7">
-        <v>60.009990000000002</v>
+        <v>60.00999</v>
       </c>
       <c r="AH7">
         <v>-125.74744</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34">
       <c r="A8">
         <v>872030.9608</v>
       </c>
@@ -1665,18 +1649,18 @@
         <v>194</v>
       </c>
       <c r="AG8">
-        <v>60.199480000000001</v>
+        <v>60.19948</v>
       </c>
       <c r="AH8">
         <v>-125.78986</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:34">
       <c r="A9">
-        <v>815902.16460000002</v>
+        <v>815902.1646</v>
       </c>
       <c r="B9">
-        <v>784649.04979999899</v>
+        <v>784649.049799999</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1721,15 +1705,15 @@
         <v>61.42595</v>
       </c>
       <c r="AH9">
-        <v>-126.57483999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-126.57484</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34">
       <c r="A10">
-        <v>778950.87620000006</v>
+        <v>778950.8762000001</v>
       </c>
       <c r="B10">
-        <v>839043.09679999901</v>
+        <v>839043.096799999</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1750,7 +1734,7 @@
         <v>200</v>
       </c>
       <c r="M10">
-        <v>39.799999999999997</v>
+        <v>39.8</v>
       </c>
       <c r="N10">
         <v>3.9</v>
@@ -1771,18 +1755,18 @@
         <v>192</v>
       </c>
       <c r="AG10">
-        <v>61.941499999999998</v>
+        <v>61.9415</v>
       </c>
       <c r="AH10">
         <v>-127.17908</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:34">
       <c r="A11">
-        <v>775727.64599999995</v>
+        <v>775727.6459999999</v>
       </c>
       <c r="B11">
-        <v>811764.51179999998</v>
+        <v>811764.5118</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1830,12 +1814,12 @@
         <v>-127.283</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:34">
       <c r="A12">
-        <v>724600.21890000103</v>
+        <v>724600.218900001</v>
       </c>
       <c r="B12">
-        <v>879786.20290000003</v>
+        <v>879786.2029</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1856,18 +1840,18 @@
         <v>192</v>
       </c>
       <c r="AG12">
-        <v>62.343000000000004</v>
+        <v>62.343</v>
       </c>
       <c r="AH12">
         <v>-128.1591</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:34">
       <c r="A13">
-        <v>686719.00929999899</v>
+        <v>686719.009299999</v>
       </c>
       <c r="B13">
-        <v>930361.79749999905</v>
+        <v>930361.7974999991</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1915,12 +1899,12 @@
         <v>-128.833</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:34">
       <c r="A14">
-        <v>670696.54109999898</v>
+        <v>670696.541099999</v>
       </c>
       <c r="B14">
-        <v>1062913.3208000001</v>
+        <v>1062913.3208</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1977,18 +1961,18 @@
         <v>194</v>
       </c>
       <c r="AG14">
-        <v>64.010999999999996</v>
+        <v>64.011</v>
       </c>
       <c r="AH14">
-        <v>-129.00361000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-129.00361</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34">
       <c r="A15">
-        <v>952004.55980000098</v>
+        <v>952004.559800001</v>
       </c>
       <c r="B15">
-        <v>780679.69559999905</v>
+        <v>780679.695599999</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -2033,15 +2017,15 @@
         <v>192</v>
       </c>
       <c r="AG15">
-        <v>61.252380000000002</v>
+        <v>61.25238</v>
       </c>
       <c r="AH15">
         <v>-124.05754</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:34">
       <c r="A16">
-        <v>697500.90040000004</v>
+        <v>697500.9004</v>
       </c>
       <c r="B16">
         <v>881243.319599999</v>
@@ -2086,18 +2070,18 @@
         <v>192</v>
       </c>
       <c r="AG16">
-        <v>62.371670000000002</v>
+        <v>62.37167</v>
       </c>
       <c r="AH16">
         <v>-128.67981</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:34">
       <c r="A17">
-        <v>722243.62120000098</v>
+        <v>722243.621200001</v>
       </c>
       <c r="B17">
-        <v>933138.52619999996</v>
+        <v>933138.5262</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -2124,7 +2108,7 @@
         <v>50.2</v>
       </c>
       <c r="O17">
-        <v>33.799999999999997</v>
+        <v>33.8</v>
       </c>
       <c r="S17">
         <v>56</v>
@@ -2139,18 +2123,18 @@
         <v>192</v>
       </c>
       <c r="AG17">
-        <v>62.821680000000001</v>
+        <v>62.82168</v>
       </c>
       <c r="AH17">
         <v>-128.1336</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:34">
       <c r="A18">
-        <v>734428.89020000002</v>
+        <v>734428.8902</v>
       </c>
       <c r="B18">
-        <v>916344.91879999998</v>
+        <v>916344.9188</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -2192,18 +2176,18 @@
         <v>192</v>
       </c>
       <c r="AG18">
-        <v>62.663800000000002</v>
+        <v>62.6638</v>
       </c>
       <c r="AH18">
-        <v>-127.91880999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-127.91881</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34">
       <c r="A19">
-        <v>648925.03949999996</v>
+        <v>648925.0395</v>
       </c>
       <c r="B19">
-        <v>821724.23169999896</v>
+        <v>821724.231699999</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -2260,18 +2244,18 @@
         <v>192</v>
       </c>
       <c r="AG19">
-        <v>61.861370000000001</v>
+        <v>61.86137</v>
       </c>
       <c r="AH19">
-        <v>-129.66928999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-129.66929</v>
+      </c>
+    </row>
+    <row r="20" spans="1:34">
       <c r="A20">
-        <v>613781.95659999899</v>
+        <v>613781.956599999</v>
       </c>
       <c r="B20">
-        <v>979010.19869999995</v>
+        <v>979010.1986999999</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -2295,15 +2279,15 @@
         <v>192</v>
       </c>
       <c r="AG20">
-        <v>63.283180000000002</v>
+        <v>63.28318</v>
       </c>
       <c r="AH20">
-        <v>-130.22963999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-130.22964</v>
+      </c>
+    </row>
+    <row r="21" spans="1:34">
       <c r="A21">
-        <v>725098.75190000003</v>
+        <v>725098.7519</v>
       </c>
       <c r="B21">
         <v>836451.0196</v>
@@ -2348,18 +2332,18 @@
         <v>192</v>
       </c>
       <c r="AG21">
-        <v>61.954909999999998</v>
+        <v>61.95491</v>
       </c>
       <c r="AH21">
         <v>-128.20613</v>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:34">
       <c r="A22">
-        <v>344595.82709999901</v>
+        <v>344595.827099999</v>
       </c>
       <c r="B22">
-        <v>712453.20200000005</v>
+        <v>712453.202</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -2392,7 +2376,7 @@
         <v>35.1</v>
       </c>
       <c r="O22">
-        <v>8.8000000000000007</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P22">
         <v>112</v>
@@ -2401,7 +2385,7 @@
         <v>1670</v>
       </c>
       <c r="S22">
-        <v>89.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="T22">
         <v>1</v>
@@ -2419,18 +2403,18 @@
         <v>193</v>
       </c>
       <c r="AG22">
-        <v>60.878900000000002</v>
+        <v>60.8789</v>
       </c>
       <c r="AH22">
-        <v>-135.36010999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-135.36011</v>
+      </c>
+    </row>
+    <row r="23" spans="1:34">
       <c r="A23">
-        <v>355686.84649999999</v>
+        <v>355686.8465</v>
       </c>
       <c r="B23">
-        <v>698883.67159999895</v>
+        <v>698883.671599999</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -2508,15 +2492,15 @@
         <v>60.76146</v>
       </c>
       <c r="AH23">
-        <v>-135.14581999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-135.14582</v>
+      </c>
+    </row>
+    <row r="24" spans="1:34">
       <c r="A24">
-        <v>356616.84019999998</v>
+        <v>356616.8402</v>
       </c>
       <c r="B24">
-        <v>697844.38130000001</v>
+        <v>697844.3813</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -2594,15 +2578,15 @@
         <v>194</v>
       </c>
       <c r="AG24">
-        <v>60.752479999999998</v>
+        <v>60.75248</v>
       </c>
       <c r="AH24">
-        <v>-135.12799999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-135.128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:34">
       <c r="A25">
-        <v>352712.62580000103</v>
+        <v>352712.625800001</v>
       </c>
       <c r="B25">
         <v>702080.192600001</v>
@@ -2671,18 +2655,18 @@
         <v>194</v>
       </c>
       <c r="AG25">
-        <v>60.789020000000001</v>
+        <v>60.78902</v>
       </c>
       <c r="AH25">
-        <v>-135.20277999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-135.20278</v>
+      </c>
+    </row>
+    <row r="26" spans="1:34">
       <c r="A26">
-        <v>352798.39030000003</v>
+        <v>352798.3903</v>
       </c>
       <c r="B26">
-        <v>702044.21979999903</v>
+        <v>702044.219799999</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -2757,18 +2741,18 @@
         <v>194</v>
       </c>
       <c r="AG26">
-        <v>60.788730000000001</v>
+        <v>60.78873</v>
       </c>
       <c r="AH26">
-        <v>-135.20117999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-135.20118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:34">
       <c r="A27">
-        <v>357671.04519999999</v>
+        <v>357671.0452</v>
       </c>
       <c r="B27">
-        <v>697114.46660000097</v>
+        <v>697114.466600001</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -2798,7 +2782,7 @@
         <v>9.4</v>
       </c>
       <c r="S27">
-        <v>8.8000000000000007</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T27">
         <v>0.2</v>
@@ -2810,7 +2794,7 @@
         <v>-19.5</v>
       </c>
       <c r="W27">
-        <v>-158.80000000000001</v>
+        <v>-158.8</v>
       </c>
       <c r="AA27" t="s">
         <v>135</v>
@@ -2825,15 +2809,15 @@
         <v>194</v>
       </c>
       <c r="AG27">
-        <v>60.746319999999997</v>
+        <v>60.74632</v>
       </c>
       <c r="AH27">
-        <v>-135.10814999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-135.10815</v>
+      </c>
+    </row>
+    <row r="28" spans="1:34">
       <c r="A28">
-        <v>337863.47729999898</v>
+        <v>337863.477299999</v>
       </c>
       <c r="B28">
         <v>957026.848999999</v>
@@ -2875,7 +2859,7 @@
         <v>40.9</v>
       </c>
       <c r="O28">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="P28">
         <v>43</v>
@@ -2908,15 +2892,15 @@
         <v>194</v>
       </c>
       <c r="AG28">
-        <v>63.067610000000002</v>
+        <v>63.06761</v>
       </c>
       <c r="AH28">
-        <v>-135.71164999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-135.71165</v>
+      </c>
+    </row>
+    <row r="29" spans="1:34">
       <c r="A29">
-        <v>262654.00770000002</v>
+        <v>262654.0077</v>
       </c>
       <c r="B29">
         <v>1033086.8814</v>
@@ -2937,7 +2921,7 @@
         <v>122</v>
       </c>
       <c r="I29">
-        <v>8.8000000000000007</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J29">
         <v>441</v>
@@ -2952,10 +2936,10 @@
         <v>0.2</v>
       </c>
       <c r="N29">
-        <v>75.900000000000006</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="O29">
-        <v>2.2999999999999998</v>
+        <v>2.3</v>
       </c>
       <c r="P29">
         <v>100</v>
@@ -2991,18 +2975,18 @@
         <v>194</v>
       </c>
       <c r="AG29">
-        <v>63.705260000000003</v>
+        <v>63.70526</v>
       </c>
       <c r="AH29">
-        <v>-137.31082000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-137.31082</v>
+      </c>
+    </row>
+    <row r="30" spans="1:34">
       <c r="A30">
-        <v>203287.19289999999</v>
+        <v>203287.1929</v>
       </c>
       <c r="B30">
-        <v>724263.87670000095</v>
+        <v>724263.876700001</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -3047,7 +3031,7 @@
         <v>332</v>
       </c>
       <c r="Q30">
-        <v>32.700000000000003</v>
+        <v>32.7</v>
       </c>
       <c r="R30">
         <v>12.4</v>
@@ -3083,18 +3067,18 @@
         <v>193</v>
       </c>
       <c r="AG30">
-        <v>60.901440000000001</v>
+        <v>60.90144</v>
       </c>
       <c r="AH30">
-        <v>-137.96969000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-137.96969</v>
+      </c>
+    </row>
+    <row r="31" spans="1:34">
       <c r="A31">
-        <v>394186.81819999998</v>
+        <v>394186.8182</v>
       </c>
       <c r="B31">
-        <v>1120341.1089000001</v>
+        <v>1120341.1089</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -3178,12 +3162,12 @@
         <v>64.55104</v>
       </c>
       <c r="AH31">
-        <v>-134.70977999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-134.70978</v>
+      </c>
+    </row>
+    <row r="32" spans="1:34">
       <c r="A32">
-        <v>380139.98670000001</v>
+        <v>380139.9867</v>
       </c>
       <c r="B32">
         <v>1127375.6861</v>
@@ -3195,13 +3179,13 @@
         <v>64</v>
       </c>
       <c r="E32">
-        <v>10.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="G32">
         <v>28</v>
       </c>
       <c r="I32">
-        <v>8.1999999999999993</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J32">
         <v>207</v>
@@ -3225,7 +3209,7 @@
         <v>125</v>
       </c>
       <c r="Q32">
-        <v>8.1999999999999993</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R32">
         <v>3</v>
@@ -3255,18 +3239,18 @@
         <v>194</v>
       </c>
       <c r="AG32">
-        <v>64.609319999999997</v>
+        <v>64.60932</v>
       </c>
       <c r="AH32">
-        <v>-135.00864999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-135.00865</v>
+      </c>
+    </row>
+    <row r="33" spans="1:34">
       <c r="A33">
-        <v>887336.29109999898</v>
+        <v>887336.291099999</v>
       </c>
       <c r="B33">
-        <v>654610.74929999898</v>
+        <v>654610.749299999</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -3344,18 +3328,18 @@
         <v>194</v>
       </c>
       <c r="AG33">
-        <v>60.198729999999998</v>
+        <v>60.19873</v>
       </c>
       <c r="AH33">
-        <v>-125.51287000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-125.51287</v>
+      </c>
+    </row>
+    <row r="34" spans="1:34">
       <c r="A34">
         <v>886736.119000001</v>
       </c>
       <c r="B34">
-        <v>654494.02390000003</v>
+        <v>654494.0239</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -3385,7 +3369,7 @@
         <v>282</v>
       </c>
       <c r="L34">
-        <v>82.9</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="M34">
         <v>18.3</v>
@@ -3394,7 +3378,7 @@
         <v>5.6</v>
       </c>
       <c r="O34">
-        <v>4.0999999999999996</v>
+        <v>4.1</v>
       </c>
       <c r="P34">
         <v>230</v>
@@ -3406,7 +3390,7 @@
         <v>3</v>
       </c>
       <c r="T34">
-        <v>5.0999999999999996</v>
+        <v>5.1</v>
       </c>
       <c r="U34">
         <v>0.6</v>
@@ -3433,18 +3417,18 @@
         <v>194</v>
       </c>
       <c r="AG34">
-        <v>60.198279999999997</v>
+        <v>60.19828</v>
       </c>
       <c r="AH34">
-        <v>-125.52384000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-125.52384</v>
+      </c>
+    </row>
+    <row r="35" spans="1:34">
       <c r="A35">
-        <v>781419.96620000002</v>
+        <v>781419.9662</v>
       </c>
       <c r="B35">
-        <v>639331.67610000097</v>
+        <v>639331.676100001</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -3519,18 +3503,18 @@
         <v>194</v>
       </c>
       <c r="AG35">
-        <v>60.152349999999998</v>
+        <v>60.15235</v>
       </c>
       <c r="AH35">
         <v>-127.43579</v>
       </c>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:34">
       <c r="A36">
-        <v>760175.30390000006</v>
+        <v>760175.3039000001</v>
       </c>
       <c r="B36">
-        <v>806792.72430000105</v>
+        <v>806792.724300001</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -3587,18 +3571,18 @@
         <v>194</v>
       </c>
       <c r="AG36">
-        <v>61.666670000000003</v>
+        <v>61.66667</v>
       </c>
       <c r="AH36">
         <v>-127.58333</v>
       </c>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:34">
       <c r="A37">
-        <v>595593.68530000001</v>
+        <v>595593.6853</v>
       </c>
       <c r="B37">
-        <v>324213.06210000103</v>
+        <v>324213.062100001</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -3625,7 +3609,7 @@
         <v>138</v>
       </c>
       <c r="M37">
-        <v>20.399999999999999</v>
+        <v>20.4</v>
       </c>
       <c r="N37">
         <v>190</v>
@@ -3658,18 +3642,18 @@
         <v>194</v>
       </c>
       <c r="AG37">
-        <v>57.404350000000001</v>
+        <v>57.40435</v>
       </c>
       <c r="AH37">
         <v>-130.91825</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:34">
       <c r="A38">
-        <v>572811.91139999998</v>
+        <v>572811.9114</v>
       </c>
       <c r="B38">
-        <v>280795.99109999998</v>
+        <v>280795.9911</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -3708,7 +3692,7 @@
         <v>145</v>
       </c>
       <c r="S38">
-        <v>69.900000000000006</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="T38">
         <v>63.4</v>
@@ -3729,15 +3713,15 @@
         <v>57.01681</v>
       </c>
       <c r="AH38">
-        <v>-131.30860999999999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-131.30861</v>
+      </c>
+    </row>
+    <row r="39" spans="1:34">
       <c r="A39">
-        <v>607236.62159999995</v>
+        <v>607236.6216</v>
       </c>
       <c r="B39">
-        <v>358937.80249999999</v>
+        <v>358937.8025</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -3785,7 +3769,7 @@
         <v>52.7</v>
       </c>
       <c r="U39">
-        <v>2.3E-2</v>
+        <v>0.023</v>
       </c>
       <c r="AC39" t="s">
         <v>136</v>
@@ -3797,18 +3781,18 @@
         <v>194</v>
       </c>
       <c r="AG39">
-        <v>57.714869999999998</v>
+        <v>57.71487</v>
       </c>
       <c r="AH39">
-        <v>-130.70947000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-130.70947</v>
+      </c>
+    </row>
+    <row r="40" spans="1:34">
       <c r="A40">
-        <v>604896.18420000002</v>
+        <v>604896.1842</v>
       </c>
       <c r="B40">
-        <v>365213.06430000102</v>
+        <v>365213.064300001</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -3868,18 +3852,18 @@
         <v>194</v>
       </c>
       <c r="AG40">
-        <v>57.772060000000003</v>
+        <v>57.77206</v>
       </c>
       <c r="AH40">
-        <v>-130.74563000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-130.74563</v>
+      </c>
+    </row>
+    <row r="41" spans="1:34">
       <c r="A41">
-        <v>354071.28339999903</v>
+        <v>354071.283399999</v>
       </c>
       <c r="B41">
-        <v>716161.38110000105</v>
+        <v>716161.381100001</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -3918,7 +3902,7 @@
         <v>126</v>
       </c>
       <c r="O41">
-        <v>2.2999999999999998</v>
+        <v>2.3</v>
       </c>
       <c r="P41">
         <v>12</v>
@@ -3933,7 +3917,7 @@
         <v>58.4</v>
       </c>
       <c r="T41">
-        <v>34.799999999999997</v>
+        <v>34.8</v>
       </c>
       <c r="U41">
         <v>9.85</v>
@@ -3960,18 +3944,18 @@
         <v>194</v>
       </c>
       <c r="AG41">
-        <v>60.915894000000002</v>
+        <v>60.915894</v>
       </c>
       <c r="AH41">
         <v>-135.18883</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:34">
       <c r="A42">
-        <v>404006.80489999999</v>
+        <v>404006.8049</v>
       </c>
       <c r="B42">
-        <v>610586.05629999901</v>
+        <v>610586.056299999</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -4025,18 +4009,18 @@
         <v>194</v>
       </c>
       <c r="AG42">
-        <v>59.983330000000002</v>
+        <v>59.98333</v>
       </c>
       <c r="AH42">
-        <v>-134.21666999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-134.21667</v>
+      </c>
+    </row>
+    <row r="43" spans="1:34">
       <c r="A43">
         <v>403429.4792</v>
       </c>
       <c r="B43">
-        <v>609026.33219999995</v>
+        <v>609026.3321999999</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -4090,18 +4074,18 @@
         <v>194</v>
       </c>
       <c r="AG43">
-        <v>59.969169999999998</v>
+        <v>59.96917</v>
       </c>
       <c r="AH43">
-        <v>-134.22622999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-134.22623</v>
+      </c>
+    </row>
+    <row r="44" spans="1:34">
       <c r="A44">
-        <v>552605.09550000005</v>
+        <v>552605.0955000001</v>
       </c>
       <c r="B44">
-        <v>165578.79250000001</v>
+        <v>165578.7925</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -4122,18 +4106,18 @@
         <v>195</v>
       </c>
       <c r="AG44">
-        <v>55.977824499999997</v>
+        <v>55.9778245</v>
       </c>
       <c r="AH44">
         <v>-131.6640596</v>
       </c>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:34">
       <c r="A45">
-        <v>558705.88910000003</v>
+        <v>558705.8891</v>
       </c>
       <c r="B45">
-        <v>160374.28559999901</v>
+        <v>160374.285599999</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -4157,15 +4141,15 @@
         <v>195</v>
       </c>
       <c r="AG45">
-        <v>55.929937899999999</v>
+        <v>55.9299379</v>
       </c>
       <c r="AH45">
-        <v>-131.56833900000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-131.568339</v>
+      </c>
+    </row>
+    <row r="46" spans="1:34">
       <c r="A46">
-        <v>590862.40819999902</v>
+        <v>590862.408199999</v>
       </c>
       <c r="B46">
         <v>153851.222100001</v>
@@ -4189,15 +4173,15 @@
         <v>55.865437</v>
       </c>
       <c r="AH46">
-        <v>-131.06049999999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-131.0605</v>
+      </c>
+    </row>
+    <row r="47" spans="1:34">
       <c r="A47">
-        <v>565171.02119999903</v>
+        <v>565171.021199999</v>
       </c>
       <c r="B47">
-        <v>193591.95199999999</v>
+        <v>193591.952</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -4224,15 +4208,15 @@
         <v>56.2296634</v>
       </c>
       <c r="AH47">
-        <v>-131.45708189999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-131.4570819</v>
+      </c>
+    </row>
+    <row r="48" spans="1:34">
       <c r="A48">
-        <v>-3404995.0951999999</v>
+        <v>-3404995.0952</v>
       </c>
       <c r="B48">
-        <v>3909352.9440000001</v>
+        <v>3909352.944</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -4256,18 +4240,18 @@
         <v>195</v>
       </c>
       <c r="AG48">
-        <v>56.675502100000003</v>
+        <v>56.6755021</v>
       </c>
       <c r="AH48">
-        <v>131.89327109999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:34" x14ac:dyDescent="0.25">
+        <v>131.8932711</v>
+      </c>
+    </row>
+    <row r="49" spans="1:34">
       <c r="A49">
-        <v>725248.70219999901</v>
+        <v>725248.702199999</v>
       </c>
       <c r="B49">
-        <v>836302.54029999999</v>
+        <v>836302.5403</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -4291,18 +4275,18 @@
         <v>192</v>
       </c>
       <c r="AG49">
-        <v>61.953490000000002</v>
+        <v>61.95349</v>
       </c>
       <c r="AH49">
-        <v>-128.20347000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-128.20347</v>
+      </c>
+    </row>
+    <row r="50" spans="1:34">
       <c r="A50">
         <v>713536.347899999</v>
       </c>
       <c r="B50">
-        <v>853570.88649999897</v>
+        <v>853570.886499999</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -4344,18 +4328,18 @@
         <v>194</v>
       </c>
       <c r="AG50">
-        <v>62.115000000000002</v>
+        <v>62.115</v>
       </c>
       <c r="AH50">
         <v>-128.405</v>
       </c>
     </row>
-    <row r="51" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:34">
       <c r="A51">
-        <v>746584.92919999897</v>
+        <v>746584.929199999</v>
       </c>
       <c r="B51">
-        <v>777121.64049999998</v>
+        <v>777121.6405</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -4409,18 +4393,18 @@
         <v>196</v>
       </c>
       <c r="AG51">
-        <v>61.410299999999999</v>
+        <v>61.4103</v>
       </c>
       <c r="AH51">
         <v>-127.88</v>
       </c>
     </row>
-    <row r="52" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:34">
       <c r="A52">
-        <v>204006.26789999899</v>
+        <v>204006.267899999</v>
       </c>
       <c r="B52">
-        <v>564618.04990000103</v>
+        <v>564618.049900001</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -4438,18 +4422,18 @@
         <v>194</v>
       </c>
       <c r="AG52">
-        <v>59.472000000000001</v>
+        <v>59.472</v>
       </c>
       <c r="AH52">
         <v>-137.715</v>
       </c>
     </row>
-    <row r="53" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:34">
       <c r="A53">
-        <v>696705.92950000102</v>
+        <v>696705.929500001</v>
       </c>
       <c r="B53">
-        <v>1079552.3197000001</v>
+        <v>1079552.3197</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -4482,7 +4466,7 @@
         <v>1.6</v>
       </c>
       <c r="P53">
-        <v>98.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="Q53">
         <v>1368</v>
@@ -4506,18 +4490,18 @@
         <v>192</v>
       </c>
       <c r="AG53">
-        <v>64.145930000000007</v>
+        <v>64.14593000000001</v>
       </c>
       <c r="AH53">
-        <v>-128.45045999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-128.45046</v>
+      </c>
+    </row>
+    <row r="54" spans="1:34">
       <c r="A54">
-        <v>706271.39000000095</v>
+        <v>706271.3900000009</v>
       </c>
       <c r="B54">
-        <v>1082536.5475000001</v>
+        <v>1082536.5475</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -4535,15 +4519,15 @@
         <v>194</v>
       </c>
       <c r="AG54">
-        <v>64.167000000000002</v>
+        <v>64.167</v>
       </c>
       <c r="AH54">
         <v>-128.25</v>
       </c>
     </row>
-    <row r="55" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:34">
       <c r="A55">
-        <v>670681.53329999896</v>
+        <v>670681.533299999</v>
       </c>
       <c r="B55">
         <v>1062688.8905</v>
@@ -4606,12 +4590,12 @@
         <v>64.009</v>
       </c>
       <c r="AH55">
-        <v>-129.00416999999999</v>
-      </c>
-    </row>
-    <row r="56" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-129.00417</v>
+      </c>
+    </row>
+    <row r="56" spans="1:34">
       <c r="A56">
-        <v>670464.97409999894</v>
+        <v>670464.9740999989</v>
       </c>
       <c r="B56">
         <v>1062676.9453</v>
@@ -4677,12 +4661,12 @@
         <v>-129.00861</v>
       </c>
     </row>
-    <row r="57" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:34">
       <c r="A57">
-        <v>698794.77659999998</v>
+        <v>698794.7766</v>
       </c>
       <c r="B57">
-        <v>1072683.6721999999</v>
+        <v>1072683.6722</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -4736,18 +4720,18 @@
         <v>194</v>
       </c>
       <c r="AG57">
-        <v>64.083330000000004</v>
+        <v>64.08333</v>
       </c>
       <c r="AH57">
-        <v>-128.41667000000001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-128.41667</v>
+      </c>
+    </row>
+    <row r="58" spans="1:34">
       <c r="A58">
         <v>403429.4792</v>
       </c>
       <c r="B58">
-        <v>609026.33219999995</v>
+        <v>609026.3321999999</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -4765,7 +4749,7 @@
         <v>85</v>
       </c>
       <c r="I58">
-        <v>8.1999999999999993</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L58">
         <v>59</v>
@@ -4801,18 +4785,18 @@
         <v>192</v>
       </c>
       <c r="AG58">
-        <v>59.969169999999998</v>
+        <v>59.96917</v>
       </c>
       <c r="AH58">
-        <v>-134.22622999999999</v>
-      </c>
-    </row>
-    <row r="59" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-134.22623</v>
+      </c>
+    </row>
+    <row r="59" spans="1:34">
       <c r="A59">
-        <v>416763.38160000002</v>
+        <v>416763.3816</v>
       </c>
       <c r="B59">
-        <v>598458.77129999897</v>
+        <v>598458.771299999</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -4836,13 +4820,13 @@
         <v>58</v>
       </c>
       <c r="M59">
-        <v>9.8000000000000007</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N59">
         <v>2.4</v>
       </c>
       <c r="O59">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="P59">
         <v>114</v>
@@ -4866,18 +4850,18 @@
         <v>192</v>
       </c>
       <c r="AG59">
-        <v>59.877209999999998</v>
+        <v>59.87721</v>
       </c>
       <c r="AH59">
-        <v>-133.98356000000001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-133.98356</v>
+      </c>
+    </row>
+    <row r="60" spans="1:34">
       <c r="A60">
         <v>438766.151000001</v>
       </c>
       <c r="B60">
-        <v>545393.61289999995</v>
+        <v>545393.6128999999</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -4895,7 +4879,7 @@
         <v>80</v>
       </c>
       <c r="I60">
-        <v>8.1999999999999993</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L60">
         <v>67</v>
@@ -4931,18 +4915,18 @@
         <v>197</v>
       </c>
       <c r="AG60">
-        <v>59.403939999999999</v>
+        <v>59.40394</v>
       </c>
       <c r="AH60">
-        <v>-133.57544999999999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-133.57545</v>
+      </c>
+    </row>
+    <row r="61" spans="1:34">
       <c r="A61">
-        <v>492939.82169999898</v>
+        <v>492939.821699999</v>
       </c>
       <c r="B61">
-        <v>530250.57069999899</v>
+        <v>530250.570699999</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -4960,18 +4944,18 @@
         <v>192</v>
       </c>
       <c r="AG61">
-        <v>59.272269999999999</v>
+        <v>59.27227</v>
       </c>
       <c r="AH61">
-        <v>-132.62351000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-132.62351</v>
+      </c>
+    </row>
+    <row r="62" spans="1:34">
       <c r="A62">
-        <v>656367.32509999897</v>
+        <v>656367.325099999</v>
       </c>
       <c r="B62">
-        <v>575049.11700000102</v>
+        <v>575049.117000001</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -4995,12 +4979,12 @@
         <v>-129.73254</v>
       </c>
     </row>
-    <row r="63" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:34">
       <c r="A63">
-        <v>870801.50450000004</v>
+        <v>870801.5045</v>
       </c>
       <c r="B63">
-        <v>575153.17820000101</v>
+        <v>575153.178200001</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -5024,18 +5008,18 @@
         <v>198</v>
       </c>
       <c r="AG63">
-        <v>59.504060000000003</v>
+        <v>59.50406</v>
       </c>
       <c r="AH63">
-        <v>-125.95632999999999</v>
-      </c>
-    </row>
-    <row r="64" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-125.95633</v>
+      </c>
+    </row>
+    <row r="64" spans="1:34">
       <c r="A64">
-        <v>927946.82979999995</v>
+        <v>927946.8297999999</v>
       </c>
       <c r="B64">
-        <v>516755.41110000003</v>
+        <v>516755.4111</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -5059,12 +5043,12 @@
         <v>-125.07669</v>
       </c>
     </row>
-    <row r="65" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:34">
       <c r="A65">
-        <v>933208.83319999999</v>
+        <v>933208.8332</v>
       </c>
       <c r="B65">
-        <v>581299.26630000002</v>
+        <v>581299.2663</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -5085,18 +5069,18 @@
         <v>192</v>
       </c>
       <c r="AG65">
-        <v>59.496299999999998</v>
+        <v>59.4963</v>
       </c>
       <c r="AH65">
         <v>-124.85186</v>
       </c>
     </row>
-    <row r="66" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:34">
       <c r="A66">
-        <v>892352.54859999905</v>
+        <v>892352.548599999</v>
       </c>
       <c r="B66">
-        <v>589627.06350000005</v>
+        <v>589627.0635</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -5117,18 +5101,18 @@
         <v>192</v>
       </c>
       <c r="AG66">
-        <v>59.612949999999998</v>
+        <v>59.61295</v>
       </c>
       <c r="AH66">
         <v>-125.55107</v>
       </c>
     </row>
-    <row r="67" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:34">
       <c r="A67">
         <v>786428.422599999</v>
       </c>
       <c r="B67">
-        <v>846634.54529999895</v>
+        <v>846634.545299999</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -5185,12 +5169,12 @@
         <v>-127.02467</v>
       </c>
     </row>
-    <row r="68" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:34">
       <c r="A68">
-        <v>697600.88729999994</v>
+        <v>697600.8872999999</v>
       </c>
       <c r="B68">
-        <v>1079617.5212000001</v>
+        <v>1079617.5212</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -5247,15 +5231,15 @@
         <v>192</v>
       </c>
       <c r="AG68">
-        <v>64.146000000000001</v>
+        <v>64.146</v>
       </c>
       <c r="AH68">
-        <v>-128.43199999999999</v>
-      </c>
-    </row>
-    <row r="69" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-128.432</v>
+      </c>
+    </row>
+    <row r="69" spans="1:34">
       <c r="A69">
-        <v>-132782.94409999999</v>
+        <v>-132782.9441</v>
       </c>
       <c r="B69">
         <v>1239975.9634</v>
@@ -5279,15 +5263,15 @@
         <v>194</v>
       </c>
       <c r="AG69">
-        <v>65.030983399999997</v>
+        <v>65.0309834</v>
       </c>
       <c r="AH69">
-        <v>-146.05243350000001</v>
-      </c>
-    </row>
-    <row r="70" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-146.0524335</v>
+      </c>
+    </row>
+    <row r="70" spans="1:34">
       <c r="A70">
-        <v>-66812.324699999794</v>
+        <v>-66812.32469999979</v>
       </c>
       <c r="B70">
         <v>1243914.1894</v>
@@ -5311,15 +5295,15 @@
         <v>199</v>
       </c>
       <c r="AG70">
-        <v>65.184661000000006</v>
+        <v>65.18466100000001</v>
       </c>
       <c r="AH70">
         <v>-144.692004</v>
       </c>
     </row>
-    <row r="71" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:34">
       <c r="A71">
-        <v>-57144.195299999803</v>
+        <v>-57144.1952999998</v>
       </c>
       <c r="B71">
         <v>1276707.7449</v>
@@ -5346,15 +5330,15 @@
         <v>194</v>
       </c>
       <c r="AG71">
-        <v>65.489453999999995</v>
+        <v>65.48945399999999</v>
       </c>
       <c r="AH71">
-        <v>-144.62231399999999</v>
-      </c>
-    </row>
-    <row r="72" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-144.622314</v>
+      </c>
+    </row>
+    <row r="72" spans="1:34">
       <c r="A72">
-        <v>21929.395999999699</v>
+        <v>21929.3959999997</v>
       </c>
       <c r="B72">
         <v>1218689.8705</v>
@@ -5378,18 +5362,18 @@
         <v>200</v>
       </c>
       <c r="AG72">
-        <v>65.102091999999999</v>
+        <v>65.102092</v>
       </c>
       <c r="AH72">
-        <v>-142.73262700000001</v>
-      </c>
-    </row>
-    <row r="73" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-142.732627</v>
+      </c>
+    </row>
+    <row r="73" spans="1:34">
       <c r="A73">
-        <v>-5595.2453000005298</v>
+        <v>-5595.24530000053</v>
       </c>
       <c r="B73">
-        <v>1153857.4432000001</v>
+        <v>1153857.4432</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -5410,13 +5394,13 @@
         <v>201</v>
       </c>
       <c r="AG73">
-        <v>64.488980999999995</v>
+        <v>64.488981</v>
       </c>
       <c r="AH73">
         <v>-143.081535</v>
       </c>
     </row>
-    <row r="74" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:34">
       <c r="A74">
         <v>-29817.8704000004</v>
       </c>
@@ -5439,15 +5423,15 @@
         <v>202</v>
       </c>
       <c r="AG74">
-        <v>60.889150999999998</v>
+        <v>60.889151</v>
       </c>
       <c r="AH74">
-        <v>-142.28966800000001</v>
-      </c>
-    </row>
-    <row r="75" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-142.289668</v>
+      </c>
+    </row>
+    <row r="75" spans="1:34">
       <c r="A75">
-        <v>209789.15779999999</v>
+        <v>209789.1578</v>
       </c>
       <c r="B75">
         <v>474269.1874</v>
@@ -5468,18 +5452,18 @@
         <v>202</v>
       </c>
       <c r="AG75">
-        <v>58.665373000000002</v>
+        <v>58.665373</v>
       </c>
       <c r="AH75">
-        <v>-137.48856599999999</v>
-      </c>
-    </row>
-    <row r="76" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-137.488566</v>
+      </c>
+    </row>
+    <row r="76" spans="1:34">
       <c r="A76">
-        <v>299332.26120000001</v>
+        <v>299332.2612</v>
       </c>
       <c r="B76">
-        <v>407958.78409999999</v>
+        <v>407958.7841</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -5500,18 +5484,18 @@
         <v>195</v>
       </c>
       <c r="AG76">
-        <v>58.122278999999999</v>
+        <v>58.122279</v>
       </c>
       <c r="AH76">
-        <v>-135.89210299999999</v>
-      </c>
-    </row>
-    <row r="77" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-135.892103</v>
+      </c>
+    </row>
+    <row r="77" spans="1:34">
       <c r="A77">
-        <v>296574.62989999901</v>
+        <v>296574.629899999</v>
       </c>
       <c r="B77">
-        <v>395148.03739999997</v>
+        <v>395148.0374</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -5532,18 +5516,18 @@
         <v>195</v>
       </c>
       <c r="AG77">
-        <v>58.005581999999997</v>
+        <v>58.005582</v>
       </c>
       <c r="AH77">
-        <v>-135.92693399999999</v>
-      </c>
-    </row>
-    <row r="78" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-135.926934</v>
+      </c>
+    </row>
+    <row r="78" spans="1:34">
       <c r="A78">
-        <v>289118.69420000003</v>
+        <v>289118.6942</v>
       </c>
       <c r="B78">
-        <v>377172.43119999999</v>
+        <v>377172.4312</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -5561,18 +5545,18 @@
         <v>195</v>
       </c>
       <c r="AG78">
-        <v>57.839992000000002</v>
+        <v>57.839992</v>
       </c>
       <c r="AH78">
-        <v>-136.03541200000001</v>
-      </c>
-    </row>
-    <row r="79" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-136.035412</v>
+      </c>
+    </row>
+    <row r="79" spans="1:34">
       <c r="A79">
         <v>299996.787799999</v>
       </c>
       <c r="B79">
-        <v>368797.54840000003</v>
+        <v>368797.5484</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -5593,18 +5577,18 @@
         <v>195</v>
       </c>
       <c r="AG79">
-        <v>57.769868000000002</v>
+        <v>57.769868</v>
       </c>
       <c r="AH79">
-        <v>-135.84598800000001</v>
-      </c>
-    </row>
-    <row r="80" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-135.845988</v>
+      </c>
+    </row>
+    <row r="80" spans="1:34">
       <c r="A80">
         <v>270810.7622</v>
       </c>
       <c r="B80">
-        <v>374472.51799999899</v>
+        <v>374472.517999999</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -5628,15 +5612,15 @@
         <v>57.806075</v>
       </c>
       <c r="AH80">
-        <v>-136.33888400000001</v>
-      </c>
-    </row>
-    <row r="81" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-136.338884</v>
+      </c>
+    </row>
+    <row r="81" spans="1:34">
       <c r="A81">
-        <v>337451.16259999899</v>
+        <v>337451.162599999</v>
       </c>
       <c r="B81">
-        <v>367917.41840000101</v>
+        <v>367917.418400001</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -5663,9 +5647,9 @@
         <v>-135.219618</v>
       </c>
     </row>
-    <row r="82" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:34">
       <c r="A82">
-        <v>323201.11150000099</v>
+        <v>323201.111500001</v>
       </c>
       <c r="B82">
         <v>265284.2194</v>
@@ -5689,15 +5673,15 @@
         <v>194</v>
       </c>
       <c r="AG82">
-        <v>56.846530999999999</v>
+        <v>56.846531</v>
       </c>
       <c r="AH82">
         <v>-135.379772</v>
       </c>
     </row>
-    <row r="83" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:34">
       <c r="A83">
-        <v>363517.24690000003</v>
+        <v>363517.2469</v>
       </c>
       <c r="B83">
         <v>249498.2849</v>
@@ -5718,18 +5702,18 @@
         <v>195</v>
       </c>
       <c r="AG83">
-        <v>56.718592000000001</v>
+        <v>56.718592</v>
       </c>
       <c r="AH83">
-        <v>-134.71472800000001</v>
-      </c>
-    </row>
-    <row r="84" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-134.714728</v>
+      </c>
+    </row>
+    <row r="84" spans="1:34">
       <c r="A84">
         <v>357889.4241</v>
       </c>
       <c r="B84">
-        <v>290789.11859999999</v>
+        <v>290789.1186</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -5750,18 +5734,18 @@
         <v>194</v>
       </c>
       <c r="AG84">
-        <v>57.089672299999997</v>
+        <v>57.0896723</v>
       </c>
       <c r="AH84">
-        <v>-134.83058969999999</v>
-      </c>
-    </row>
-    <row r="85" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-134.8305897</v>
+      </c>
+    </row>
+    <row r="85" spans="1:34">
       <c r="A85">
-        <v>527589.30959999899</v>
+        <v>527589.309599999</v>
       </c>
       <c r="B85">
-        <v>248123.57929999899</v>
+        <v>248123.579299999</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -5782,15 +5766,15 @@
         <v>194</v>
       </c>
       <c r="AG85">
-        <v>56.726835999999999</v>
+        <v>56.726836</v>
       </c>
       <c r="AH85">
-        <v>-132.05231000000001</v>
-      </c>
-    </row>
-    <row r="86" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-132.05231</v>
+      </c>
+    </row>
+    <row r="86" spans="1:34">
       <c r="A86">
-        <v>515224.80910000001</v>
+        <v>515224.8091</v>
       </c>
       <c r="B86">
         <v>239633.999199999</v>
@@ -5811,15 +5795,15 @@
         <v>202</v>
       </c>
       <c r="AG86">
-        <v>56.650697600000001</v>
+        <v>56.6506976</v>
       </c>
       <c r="AH86">
         <v>-132.2534895</v>
       </c>
     </row>
-    <row r="87" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:34">
       <c r="A87">
-        <v>518633.29880000098</v>
+        <v>518633.298800001</v>
       </c>
       <c r="B87">
         <v>246078.479599999</v>
@@ -5846,18 +5830,18 @@
         <v>202</v>
       </c>
       <c r="AG87">
-        <v>56.708827100000001</v>
+        <v>56.7088271</v>
       </c>
       <c r="AH87">
-        <v>-132.19780040000001</v>
-      </c>
-    </row>
-    <row r="88" spans="1:34" x14ac:dyDescent="0.25">
+        <v>-132.1978004</v>
+      </c>
+    </row>
+    <row r="88" spans="1:34">
       <c r="A88">
         <v>493647.848999999</v>
       </c>
       <c r="B88">
-        <v>218200.45570000101</v>
+        <v>218200.455700001</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -5875,15 +5859,15 @@
         <v>202</v>
       </c>
       <c r="AG88">
-        <v>56.457094499999997</v>
+        <v>56.4570945</v>
       </c>
       <c r="AH88">
         <v>-132.6023179</v>
       </c>
     </row>
-    <row r="89" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:34">
       <c r="A89">
-        <v>595398.46620000002</v>
+        <v>595398.4662</v>
       </c>
       <c r="B89">
         <v>185203.157600001</v>
@@ -5904,82 +5888,82 @@
         <v>195</v>
       </c>
       <c r="AG89">
-        <v>56.148227599999998</v>
+        <v>56.1482276</v>
       </c>
       <c r="AH89">
-        <v>-130.97673130000001</v>
+        <v>-130.9767313</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AD2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="AD3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="AD4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="AD9" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="AD10" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="AD11" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="AD12" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="AD13" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="AD14" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="AD15" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="AD16" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="AD17" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="AD18" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="AD19" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="AD21" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="AD22" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="AD27" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="AD36" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="AD37" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="AD38" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="AD39" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="AD40" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="AD42" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="AD43" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="AD44" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="AD45" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="AD46" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="AD47" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="AD48" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="AD49" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="AD50" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="AD51" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="AD52" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="AD53" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="AD55" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="AD56" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="AD57" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="AD58" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="AD59" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="AD60" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="AD61" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="AD62" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="AD63" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="AD64" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="AD65" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="AD67" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="AD68" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="AD69" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="AD70" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="AD71" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="AD72" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="AD73" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="AD74" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="AD75" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="AD76" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="AD77" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="AD78" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="AD79" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="AD80" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="AD81" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="AD82" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="AD83" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="AD84" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="AD85" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="AD86" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="AD87" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="AD88" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="AD89" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="AD2" r:id="rId1"/>
+    <hyperlink ref="AD3" r:id="rId2"/>
+    <hyperlink ref="AD4" r:id="rId3"/>
+    <hyperlink ref="AD9" r:id="rId4"/>
+    <hyperlink ref="AD10" r:id="rId5"/>
+    <hyperlink ref="AD11" r:id="rId6"/>
+    <hyperlink ref="AD12" r:id="rId7"/>
+    <hyperlink ref="AD13" r:id="rId8"/>
+    <hyperlink ref="AD14" r:id="rId9"/>
+    <hyperlink ref="AD15" r:id="rId10"/>
+    <hyperlink ref="AD16" r:id="rId11"/>
+    <hyperlink ref="AD17" r:id="rId12"/>
+    <hyperlink ref="AD18" r:id="rId13"/>
+    <hyperlink ref="AD19" r:id="rId14"/>
+    <hyperlink ref="AD21" r:id="rId15"/>
+    <hyperlink ref="AD22" r:id="rId16"/>
+    <hyperlink ref="AD27" r:id="rId17"/>
+    <hyperlink ref="AD36" r:id="rId18"/>
+    <hyperlink ref="AD37" r:id="rId19"/>
+    <hyperlink ref="AD38" r:id="rId20"/>
+    <hyperlink ref="AD39" r:id="rId21"/>
+    <hyperlink ref="AD40" r:id="rId22"/>
+    <hyperlink ref="AD42" r:id="rId23"/>
+    <hyperlink ref="AD43" r:id="rId24"/>
+    <hyperlink ref="AD44" r:id="rId25"/>
+    <hyperlink ref="AD45" r:id="rId26"/>
+    <hyperlink ref="AD46" r:id="rId27"/>
+    <hyperlink ref="AD47" r:id="rId28"/>
+    <hyperlink ref="AD48" r:id="rId29"/>
+    <hyperlink ref="AD49" r:id="rId30"/>
+    <hyperlink ref="AD50" r:id="rId31"/>
+    <hyperlink ref="AD51" r:id="rId32"/>
+    <hyperlink ref="AD52" r:id="rId33"/>
+    <hyperlink ref="AD53" r:id="rId34"/>
+    <hyperlink ref="AD55" r:id="rId35"/>
+    <hyperlink ref="AD56" r:id="rId36"/>
+    <hyperlink ref="AD57" r:id="rId37"/>
+    <hyperlink ref="AD58" r:id="rId38"/>
+    <hyperlink ref="AD59" r:id="rId39"/>
+    <hyperlink ref="AD60" r:id="rId40"/>
+    <hyperlink ref="AD61" r:id="rId41"/>
+    <hyperlink ref="AD62" r:id="rId42"/>
+    <hyperlink ref="AD63" r:id="rId43"/>
+    <hyperlink ref="AD64" r:id="rId44"/>
+    <hyperlink ref="AD65" r:id="rId45"/>
+    <hyperlink ref="AD67" r:id="rId46"/>
+    <hyperlink ref="AD68" r:id="rId47"/>
+    <hyperlink ref="AD69" r:id="rId48"/>
+    <hyperlink ref="AD70" r:id="rId49"/>
+    <hyperlink ref="AD71" r:id="rId50"/>
+    <hyperlink ref="AD72" r:id="rId51"/>
+    <hyperlink ref="AD73" r:id="rId52"/>
+    <hyperlink ref="AD74" r:id="rId53"/>
+    <hyperlink ref="AD75" r:id="rId54"/>
+    <hyperlink ref="AD76" r:id="rId55"/>
+    <hyperlink ref="AD77" r:id="rId56"/>
+    <hyperlink ref="AD78" r:id="rId57"/>
+    <hyperlink ref="AD79" r:id="rId58"/>
+    <hyperlink ref="AD80" r:id="rId59"/>
+    <hyperlink ref="AD81" r:id="rId60"/>
+    <hyperlink ref="AD82" r:id="rId61"/>
+    <hyperlink ref="AD83" r:id="rId62"/>
+    <hyperlink ref="AD84" r:id="rId63"/>
+    <hyperlink ref="AD85" r:id="rId64"/>
+    <hyperlink ref="AD86" r:id="rId65"/>
+    <hyperlink ref="AD87" r:id="rId66"/>
+    <hyperlink ref="AD88" r:id="rId67"/>
+    <hyperlink ref="AD89" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
